--- a/benchmarks/XGBOOST_V3_FORECASTING/xgb_results.xlsx
+++ b/benchmarks/XGBOOST_V3_FORECASTING/xgb_results.xlsx
@@ -473,13 +473,13 @@
         <v>2021</v>
       </c>
       <c r="D2" t="n">
-        <v>5.766032695770264</v>
+        <v>5.874279975891113</v>
       </c>
       <c r="E2" t="n">
-        <v>24.27626110065847</v>
+        <v>25.70667837329983</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7447975277900696</v>
+        <v>0.7182669043540955</v>
       </c>
     </row>
     <row r="3">
@@ -493,13 +493,13 @@
         <v>2022</v>
       </c>
       <c r="D3" t="n">
-        <v>14.0371036529541</v>
+        <v>14.42225170135498</v>
       </c>
       <c r="E3" t="n">
-        <v>56.39156448372287</v>
+        <v>59.01722595127947</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7732700109481812</v>
+        <v>0.7584477663040161</v>
       </c>
     </row>
     <row r="4">
@@ -513,13 +513,13 @@
         <v>2023</v>
       </c>
       <c r="D4" t="n">
-        <v>16.39470291137695</v>
+        <v>14.55582618713379</v>
       </c>
       <c r="E4" t="n">
-        <v>64.59387094812092</v>
+        <v>56.57153544890642</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7216163277626038</v>
+        <v>0.7772179245948792</v>
       </c>
     </row>
     <row r="5">
@@ -533,13 +533,13 @@
         <v>2024</v>
       </c>
       <c r="D5" t="n">
-        <v>37.36521148681641</v>
+        <v>35.24965667724609</v>
       </c>
       <c r="E5" t="n">
-        <v>122.5008051631703</v>
+        <v>118.6954521098534</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7820809483528137</v>
+        <v>0.8012843728065491</v>
       </c>
     </row>
     <row r="6">
@@ -553,13 +553,13 @@
         <v>2025</v>
       </c>
       <c r="D6" t="n">
-        <v>17.04785346984863</v>
+        <v>15.22810840606689</v>
       </c>
       <c r="E6" t="n">
-        <v>49.40578549750019</v>
+        <v>46.49101318148084</v>
       </c>
       <c r="F6" t="n">
-        <v>0.815893292427063</v>
+        <v>0.8369758129119873</v>
       </c>
     </row>
   </sheetData>
@@ -600,10 +600,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>18.12218084335327</v>
+        <v>17.06602458953857</v>
       </c>
       <c r="C2" t="n">
-        <v>11.65970454549263</v>
+        <v>10.86931679545006</v>
       </c>
     </row>
     <row r="3">
@@ -613,10 +613,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>63.43365743863454</v>
+        <v>61.29638101296401</v>
       </c>
       <c r="C3" t="n">
-        <v>36.29720370790132</v>
+        <v>34.66986417189428</v>
       </c>
     </row>
     <row r="4">
@@ -626,10 +626,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.7675316214561463</v>
+        <v>0.7784385561943055</v>
       </c>
       <c r="C4" t="n">
-        <v>0.03608502617426586</v>
+        <v>0.04463824332293643</v>
       </c>
     </row>
   </sheetData>
@@ -643,7 +643,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B69"/>
+  <dimension ref="A1:B67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -665,97 +665,97 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.1580124795436859</v>
+        <v>0.1487991511821747</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>pop</t>
+          <t>area_km2</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.08891962468624115</v>
+        <v>0.07902226597070694</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>population_total</t>
+          <t>pop</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.06853814423084259</v>
+        <v>0.06984539330005646</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>casos_roll4_mean</t>
+          <t>population_total</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.03836413472890854</v>
+        <v>0.06939093768596649</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>casos_lag_2</t>
+          <t>population_density</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.03796514868736267</v>
+        <v>0.06525184214115143</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Rt_lag_1</t>
+          <t>casos_roll4_mean</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.02873520180583</v>
+        <v>0.04901425167918205</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>area_km2</t>
+          <t>casos_lag_2</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.02714139595627785</v>
+        <v>0.03897804766893387</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Rt_lag_2</t>
+          <t>Rt_lag_1</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.02111566811800003</v>
+        <v>0.02545414492487907</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>population_density</t>
+          <t>tempmed_lag_1</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.02012968249619007</v>
+        <v>0.0151049243286252</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Rt_lag_4</t>
+          <t>Rt_lag_2</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.01781653799116611</v>
+        <v>0.01507250498980284</v>
       </c>
     </row>
     <row r="12">
@@ -765,577 +765,557 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.01696188934147358</v>
+        <v>0.01254058349877596</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>precip_total_semana_lag_1</t>
+          <t>n_pixels</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.01687345840036869</v>
+        <v>0.01243518851697445</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>casos_roll8_mean</t>
+          <t>tempmed_roll8_mean</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.01567944511771202</v>
+        <v>0.0114244781434536</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>precip_roll4_sum</t>
+          <t>NDVI_std</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.0123544204980135</v>
+        <v>0.01133645419031382</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>casos_lag_8</t>
+          <t>tempmed_roll4_mean</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.01197607256472111</v>
+        <v>0.01119090151041746</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>elev_max</t>
+          <t>precip_roll4_sum</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.01168220024555922</v>
+        <v>0.01116539258509874</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>pct_wetland</t>
+          <t>precip_media_semana</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.01156247220933437</v>
+        <v>0.01068156398832798</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>tempmed_roll4_mean</t>
+          <t>Rt_lag_4</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.0107548926025629</v>
+        <v>0.01050150115042925</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>water_supply_pct</t>
+          <t>precip_total_semana_lag_4</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.0105253616347909</v>
+        <v>0.01001084968447685</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>pct_bare_sparse</t>
+          <t>umidmed_lag_4</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.01038306392729282</v>
+        <v>0.009982230141758919</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>median_age</t>
+          <t>precip_total_semana_lag_1</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.01032019685953856</v>
+        <v>0.009869338944554329</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>pct_cropland</t>
+          <t>EVI_mean</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.01004541479051113</v>
+        <v>0.009580839425325394</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>sex_ratio</t>
+          <t>pct_wetland</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.01002511568367481</v>
+        <v>0.009502199478447437</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>male_population_pct</t>
+          <t>pct_builtup</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.009775365702807903</v>
+        <v>0.009397508576512337</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>pct_builtup</t>
+          <t>LST_Night_std</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.00963255763053894</v>
+        <v>0.009374985471367836</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>n_pixels</t>
+          <t>pct_shrubland</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.009497592225670815</v>
+        <v>0.009167383424937725</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>precip_total_semana_lag_4</t>
+          <t>garbage_collection_pct</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.009485542774200439</v>
+        <v>0.00892943236976862</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>precip_total_semana</t>
+          <t>median_age</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.009463289752602577</v>
+        <v>0.008918222039937973</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>elev_mean</t>
+          <t>precip_max_semana</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.009446408599615097</v>
+        <v>0.008737167343497276</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>umidmed_lag_4</t>
+          <t>pct_cropland</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.009397546760737896</v>
+        <v>0.00856044702231884</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>tempmed_lag_1</t>
+          <t>pct_grassland</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.009394985623657703</v>
+        <v>0.008516470901668072</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>LST_Day_mean</t>
+          <t>casos_lag_4</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.009292931295931339</v>
+        <v>0.008059308864176273</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>precip_max_semana</t>
+          <t>NDVI_mean</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.009265916422009468</v>
+        <v>0.008033525198698044</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>semana</t>
+          <t>soi</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.009068986400961876</v>
+        <v>0.007989419624209404</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>aging_index</t>
+          <t>pct_bare_sparse</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.008562971837818623</v>
+        <v>0.007930983789265156</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>tempmed_lag_4</t>
+          <t>LST_Day_mean</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.008542083203792572</v>
+        <v>0.007921158336102962</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>n_tiles</t>
+          <t>precip_roll8_sum</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.008496562018990517</v>
+        <v>0.007840188220143318</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>anio</t>
+          <t>elev_mean</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.008084484376013279</v>
+        <v>0.007808926049619913</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>tempmax</t>
+          <t>precip_total_semana</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.007927941158413887</v>
+        <v>0.007777583785355091</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>NDVI_mean</t>
+          <t>sex_ratio</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.007844550535082817</v>
+        <v>0.007636247668415308</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>tempmed_roll8_mean</t>
+          <t>tempmed_lag_4</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.00782810989767313</v>
+        <v>0.007551945745944977</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>umidmed_lag_1</t>
+          <t>male_population_pct</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.007753404788672924</v>
+        <v>0.007262258790433407</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>precip_media_semana</t>
+          <t>female_population_pct</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.007689440157264471</v>
+        <v>0.00725493673235178</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>EVI_mean</t>
+          <t>LST_Night_mean</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.0075899763032794</v>
+        <v>0.006756395101547241</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>female_population_pct</t>
+          <t>aging_index</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.007433032151311636</v>
+        <v>0.006634274031966925</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>NDVI_std</t>
+          <t>casos_lag_8</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.007408633828163147</v>
+        <v>0.006621246226131916</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>precip_roll8_sum</t>
+          <t>elev_min</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.007373684551566839</v>
+        <v>0.006309413816779852</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>casos_lag_4</t>
+          <t>casos_roll8_mean</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.007324579171836376</v>
+        <v>0.006223347038030624</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>pct_grassland</t>
+          <t>pct_water</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.007121617905795574</v>
+        <v>0.006178154610097408</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>tempmin</t>
+          <t>pct_tree_cover</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.007116533815860748</v>
+        <v>0.00595795176923275</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>LST_Night_mean</t>
+          <t>water_supply_pct</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.006966738495975733</v>
+        <v>0.005954237189143896</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>soi</t>
+          <t>elev_max</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.006921812891960144</v>
+        <v>0.00585531210526824</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>pct_tree_cover</t>
+          <t>EVI_std</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.006916625890880823</v>
+        <v>0.005783158354461193</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>garbage_collection_pct</t>
+          <t>LST_Day_std</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.006878337357193232</v>
+        <v>0.005177919287234545</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>LST_Day_std</t>
+          <t>sewage_pct</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.006704197265207767</v>
+        <v>0.004910551942884922</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>EVI_std</t>
+          <t>tempmin</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.006694720592349768</v>
+        <v>0.004880080930888653</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>tempmed</t>
+          <t>nino34</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.006531625986099243</v>
+        <v>0.004873421974480152</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>elev_min</t>
+          <t>umidmed_lag_1</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.006521976087242365</v>
+        <v>0.004823813680559397</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>LST_Night_std</t>
+          <t>tempmed</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.006483642850071192</v>
+        <v>0.004794775974005461</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>umidmed</t>
+          <t>dias_lluvia_semana</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.00631042430177331</v>
+        <v>0.004768908955156803</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>umidmax</t>
+          <t>umidmed</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.005771088413894176</v>
+        <v>0.00475464528426528</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>pct_shrubland</t>
+          <t>umidmin</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.005702557507902384</v>
+        <v>0.004710067063570023</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>sewage_pct</t>
+          <t>umidmax</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.005652898456901312</v>
+        <v>0.004671567585319281</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>dias_lluvia_semana</t>
+          <t>tempmax</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.005507918074727058</v>
+        <v>0.004542379640042782</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>pct_water</t>
+          <t>n_tiles</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.005400088615715504</v>
+        <v>0.002653443953022361</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>nino34</t>
+          <t>pct_mangroves</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.005369800142943859</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>umidmin</t>
-        </is>
-      </c>
-      <c r="B68" t="n">
-        <v>0.004997066222131252</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>pct_mangroves</t>
-        </is>
-      </c>
-      <c r="B69" t="n">
-        <v>0.0009677332127466798</v>
+        <v>0.001341876341030002</v>
       </c>
     </row>
   </sheetData>
